--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 2 Sjednica" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 2 Hamzići" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REKAPITULACIJA LOT 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="LOT 2 Sjednica" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LOT 2 Hamzići" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="REKAPITULACIJA LOT 2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'LOT 2 Sjednica'!$8:$9</definedName>

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
@@ -13,9 +13,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'LOT 2 Sjednica'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LOT 2 Sjednica'!$A$1:$F$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LOT 2 Sjednica'!$A$1:$F$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'LOT 2 Hamzići'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'LOT 2 Hamzići'!$A$1:$F$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'LOT 2 Hamzići'!$A$1:$F$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'REKAPITULACIJA LOT 2'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1238,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.73" customWidth="1" style="91" min="1" max="1"/>
@@ -2436,79 +2436,87 @@
       </c>
     </row>
     <row r="56" s="92">
-      <c r="A56" s="135" t="n"/>
-      <c r="B56" s="167" t="inlineStr">
+      <c r="A56" s="128" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="B56" s="161" t="inlineStr">
+        <is>
+          <t>Preuzimanje opreme Kupca u skladištu BH Telecom d.d. AZIĆI, Bojnička bb, Sarajevo, transport do lokacije, istovar i unos do mjesta ugradnje.
+OPREMA KUPCA (posebna nabavka): fotonaponski moduli iPV585-M2A (12 kom), PVDB 500-15-2B, ispravljači iSSU S4875G2, baterijski moduli LFP i ormar hibridnog sistema ICC360-HA1-C1 sa pripadajućim modulima. Tačan spisak i mase Kupac daje uz narudžbu.
+Stavka obuhvata:
+ - utovar u skladištu, osiguranje i učvršćenje tereta, prevoz zatvorenim ili natkrivenim vozilom, istovar na lokaciji i unos do mjesta ugradnje
+ - vozilo prilagođeno pristupnom putu lokacije (makadam) — Ponuđač ga bira pri obilasku lokacije
+ - rukovanje prema uputstvu proizvođača: FN moduli u originalnoj ambalaži i uspravno, bez oslanjanja na staklo; baterijski moduli uz zaštitu polova i dozvoljenu temperaturu; ormar bez udara i naginjanja preko dozvoljenog ugla
+ - najava skladištu najmanje 3 radna dana prije preuzimanja; prevoz usklađen sa dinamikom montaže — oprema se na lokaciji ne skladišti duže nego što montaža traži
+ - otpremnica skladišta pri preuzimanju i zapisnik o preuzimanju opreme na lokaciji (spisak, količine, stanje ambalaže, serijski brojevi), potpisan od Ponuđača i Kupca
+Od potpisa otpremnice do zapisnika o primopredaji radova za opremu odgovara Ponuđač. Zahtjevi: Prilog I, Tačka 4.9.</t>
+        </is>
+      </c>
+      <c r="C56" s="128" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D56" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="131" t="n"/>
+      <c r="F56" s="131">
+        <f>IF(AND(D56&lt;&gt;"",E56&lt;&gt;""),D56*E56,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" s="92">
+      <c r="A57" s="135" t="n"/>
+      <c r="B57" s="167" t="inlineStr">
         <is>
           <t>UKUPNO 5 — ELEKTROMONTAŽNI RADOVI:</t>
         </is>
       </c>
-      <c r="C56" s="168" t="n"/>
-      <c r="D56" s="168" t="n"/>
-      <c r="E56" s="137" t="n"/>
-      <c r="F56" s="138">
-        <f>SUM(F39:F55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58" s="92">
-      <c r="A58" s="125" t="inlineStr">
+      <c r="C57" s="168" t="n"/>
+      <c r="D57" s="168" t="n"/>
+      <c r="E57" s="137" t="n"/>
+      <c r="F57" s="138">
+        <f>SUM(F39:F56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59" s="92">
+      <c r="A59" s="125" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B58" s="159" t="inlineStr">
+      <c r="B59" s="159" t="inlineStr">
         <is>
           <t>PUŠTANJE U RAD, OBUKA I DOKUMENTACIJA (DO POTPUNE GOTOVOSTI)</t>
         </is>
       </c>
-      <c r="C58" s="160" t="n"/>
-      <c r="D58" s="160" t="n"/>
-      <c r="E58" s="127" t="n"/>
-      <c r="F58" s="127" t="n"/>
-    </row>
-    <row r="59" s="92">
-      <c r="A59" s="162" t="n"/>
-      <c r="B59" s="169" t="n"/>
-      <c r="C59" s="168" t="n"/>
-      <c r="D59" s="168" t="n"/>
-      <c r="E59" s="137" t="n"/>
-      <c r="F59" s="162" t="n"/>
+      <c r="C59" s="160" t="n"/>
+      <c r="D59" s="160" t="n"/>
+      <c r="E59" s="127" t="n"/>
+      <c r="F59" s="127" t="n"/>
     </row>
     <row r="60" s="92">
-      <c r="A60" s="128" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B60" s="161" t="inlineStr">
-        <is>
-          <t>Puštanje u rad kompletnog sistema, funkcionalno testiranje automatskog starta DEA po kriteriju stanja baterija, testiranje prelaska izvora i 72-satni probni rad sa zapisom parametara.</t>
-        </is>
-      </c>
-      <c r="C60" s="128" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="D60" s="128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="131" t="n"/>
-      <c r="F60" s="131">
-        <f>IF(AND(D60&lt;&gt;"",E60&lt;&gt;""),D60*E60,"")</f>
-        <v/>
-      </c>
+      <c r="A60" s="162" t="n"/>
+      <c r="B60" s="169" t="n"/>
+      <c r="C60" s="168" t="n"/>
+      <c r="D60" s="168" t="n"/>
+      <c r="E60" s="137" t="n"/>
+      <c r="F60" s="162" t="n"/>
     </row>
     <row r="61" s="92">
       <c r="A61" s="128" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B61" s="161" t="inlineStr">
         <is>
-          <t>Uvezivanje kontrolera DEA u krovni sistem nadzora i upravljanja BH Telecom-a (NetEco Management System), sa isporukom licenciranog softverskog paketa, instalacijom u nadzornom centru, uvezivanjem do najbližeg switcha i testiranjem prosljeđivanja alarma.</t>
+          <t>Puštanje u rad kompletnog sistema, funkcionalno testiranje automatskog starta DEA po kriteriju stanja baterija, testiranje prelaska izvora i 72-satni probni rad sa zapisom parametara.</t>
         </is>
       </c>
       <c r="C61" s="128" t="inlineStr">
@@ -2528,12 +2536,12 @@
     <row r="62" s="92">
       <c r="A62" s="128" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B62" s="161" t="inlineStr">
         <is>
-          <t>Obuka osoblja Investitora (do 4 osobe) za rukovanje i osnovno održavanje sistema, u trajanju od min. 1 radnog dana.</t>
+          <t>Uvezivanje kontrolera DEA u krovni sistem nadzora i upravljanja BH Telecom-a (NetEco Management System), sa isporukom licenciranog softverskog paketa, instalacijom u nadzornom centru, uvezivanjem do najbližeg switcha i testiranjem prosljeđivanja alarma.</t>
         </is>
       </c>
       <c r="C62" s="128" t="inlineStr">
@@ -2553,12 +2561,12 @@
     <row r="63" s="92">
       <c r="A63" s="128" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B63" s="161" t="inlineStr">
         <is>
-          <t>Izrada dokumentacije izvedenog stanja za kompletan LOT 2 (elektro, mašinski i građevinski dio), u 3 štampana primjerka i u elektronskoj formi (PDF + izvorni DWG/DOCX).</t>
+          <t>Obuka osoblja Investitora (do 4 osobe) za rukovanje i osnovno održavanje sistema, u trajanju od min. 1 radnog dana.</t>
         </is>
       </c>
       <c r="C63" s="128" t="inlineStr">
@@ -2576,33 +2584,58 @@
       </c>
     </row>
     <row r="64" s="92">
-      <c r="A64" s="135" t="n"/>
-      <c r="B64" s="167" t="inlineStr">
+      <c r="A64" s="128" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B64" s="161" t="inlineStr">
+        <is>
+          <t>Izrada dokumentacije izvedenog stanja za kompletan LOT 2 (elektro, mašinski i građevinski dio), u 3 štampana primjerka i u elektronskoj formi (PDF + izvorni DWG/DOCX).</t>
+        </is>
+      </c>
+      <c r="C64" s="128" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D64" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="131" t="n"/>
+      <c r="F64" s="131">
+        <f>IF(AND(D64&lt;&gt;"",E64&lt;&gt;""),D64*E64,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" s="92">
+      <c r="A65" s="135" t="n"/>
+      <c r="B65" s="167" t="inlineStr">
         <is>
           <t>UKUPNO 6 — PUŠTANJE U RAD, OBUKA I DOKUMENTACIJA:</t>
         </is>
       </c>
-      <c r="C64" s="168" t="n"/>
-      <c r="D64" s="168" t="n"/>
-      <c r="E64" s="137" t="n"/>
-      <c r="F64" s="138">
-        <f>SUM(F60:F63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66" s="92">
-      <c r="A66" s="170" t="n"/>
-      <c r="B66" s="171" t="inlineStr">
+      <c r="C65" s="168" t="n"/>
+      <c r="D65" s="168" t="n"/>
+      <c r="E65" s="137" t="n"/>
+      <c r="F65" s="138">
+        <f>SUM(F61:F64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67" s="92">
+      <c r="A67" s="170" t="n"/>
+      <c r="B67" s="171" t="inlineStr">
         <is>
           <t>UKUPNO LOT 2 — BS SJEDNICA (bez PDV-a):</t>
         </is>
       </c>
-      <c r="C66" s="168" t="n"/>
-      <c r="D66" s="168" t="n"/>
-      <c r="E66" s="137" t="n"/>
-      <c r="F66" s="172">
-        <f>F36+F56+F64</f>
+      <c r="C67" s="168" t="n"/>
+      <c r="D67" s="168" t="n"/>
+      <c r="E67" s="137" t="n"/>
+      <c r="F67" s="172">
+        <f>F36+F57+F65</f>
         <v/>
       </c>
     </row>
@@ -2631,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.73" customWidth="1" style="91" min="1" max="1"/>
@@ -3856,79 +3889,87 @@
       </c>
     </row>
     <row r="57" s="92">
-      <c r="A57" s="135" t="n"/>
-      <c r="B57" s="167" t="inlineStr">
+      <c r="A57" s="128" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="B57" s="161" t="inlineStr">
+        <is>
+          <t>Preuzimanje opreme Kupca u skladištu BH Telecom d.d. AZIĆI, Bojnička bb, Sarajevo, transport do lokacije, istovar i unos do mjesta ugradnje.
+OPREMA KUPCA (posebna nabavka): fotonaponski moduli iPV585-M2A (12 kom), PVDB 500-15-2B, ispravljači iSSU S4875G2, baterijski moduli LFP i ormar hibridnog sistema ICC360-HA1-C1 sa pripadajućim modulima. Tačan spisak i mase Kupac daje uz narudžbu.
+Stavka obuhvata:
+ - utovar u skladištu, osiguranje i učvršćenje tereta, prevoz zatvorenim ili natkrivenim vozilom, istovar na lokaciji i unos do mjesta ugradnje
+ - vozilo prilagođeno pristupnom putu lokacije (makadam) — Ponuđač ga bira pri obilasku lokacije
+ - rukovanje prema uputstvu proizvođača: FN moduli u originalnoj ambalaži i uspravno, bez oslanjanja na staklo; baterijski moduli uz zaštitu polova i dozvoljenu temperaturu; ormar bez udara i naginjanja preko dozvoljenog ugla
+ - najava skladištu najmanje 3 radna dana prije preuzimanja; prevoz usklađen sa dinamikom montaže — oprema se na lokaciji ne skladišti duže nego što montaža traži
+ - otpremnica skladišta pri preuzimanju i zapisnik o preuzimanju opreme na lokaciji (spisak, količine, stanje ambalaže, serijski brojevi), potpisan od Ponuđača i Kupca
+Od potpisa otpremnice do zapisnika o primopredaji radova za opremu odgovara Ponuđač. Zahtjevi: Prilog I, Tačka 4.9.</t>
+        </is>
+      </c>
+      <c r="C57" s="128" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D57" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="131" t="n"/>
+      <c r="F57" s="131">
+        <f>IF(AND(D57&lt;&gt;"",E57&lt;&gt;""),D57*E57,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" s="92">
+      <c r="A58" s="135" t="n"/>
+      <c r="B58" s="167" t="inlineStr">
         <is>
           <t>UKUPNO 5 — ELEKTROMONTAŽNI RADOVI:</t>
         </is>
       </c>
-      <c r="C57" s="168" t="n"/>
-      <c r="D57" s="168" t="n"/>
-      <c r="E57" s="137" t="n"/>
-      <c r="F57" s="138">
-        <f>SUM(F39:F56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59" s="92">
-      <c r="A59" s="125" t="inlineStr">
+      <c r="C58" s="168" t="n"/>
+      <c r="D58" s="168" t="n"/>
+      <c r="E58" s="137" t="n"/>
+      <c r="F58" s="138">
+        <f>SUM(F39:F57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60" s="92">
+      <c r="A60" s="125" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B59" s="159" t="inlineStr">
+      <c r="B60" s="159" t="inlineStr">
         <is>
           <t>PUŠTANJE U RAD, OBUKA I DOKUMENTACIJA (DO POTPUNE GOTOVOSTI)</t>
         </is>
       </c>
-      <c r="C59" s="160" t="n"/>
-      <c r="D59" s="160" t="n"/>
-      <c r="E59" s="127" t="n"/>
-      <c r="F59" s="127" t="n"/>
-    </row>
-    <row r="60" s="92">
-      <c r="A60" s="162" t="n"/>
-      <c r="B60" s="169" t="n"/>
-      <c r="C60" s="168" t="n"/>
-      <c r="D60" s="168" t="n"/>
-      <c r="E60" s="137" t="n"/>
-      <c r="F60" s="162" t="n"/>
+      <c r="C60" s="160" t="n"/>
+      <c r="D60" s="160" t="n"/>
+      <c r="E60" s="127" t="n"/>
+      <c r="F60" s="127" t="n"/>
     </row>
     <row r="61" s="92">
-      <c r="A61" s="128" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B61" s="161" t="inlineStr">
-        <is>
-          <t>Puštanje u rad kompletnog sistema, funkcionalno testiranje automatskog starta DEA po kriteriju stanja baterija, testiranje prelaska izvora i 72-satni probni rad sa zapisom parametara.</t>
-        </is>
-      </c>
-      <c r="C61" s="128" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="D61" s="128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="131" t="n"/>
-      <c r="F61" s="131">
-        <f>IF(AND(D61&lt;&gt;"",E61&lt;&gt;""),D61*E61,"")</f>
-        <v/>
-      </c>
+      <c r="A61" s="162" t="n"/>
+      <c r="B61" s="169" t="n"/>
+      <c r="C61" s="168" t="n"/>
+      <c r="D61" s="168" t="n"/>
+      <c r="E61" s="137" t="n"/>
+      <c r="F61" s="162" t="n"/>
     </row>
     <row r="62" s="92">
       <c r="A62" s="128" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B62" s="161" t="inlineStr">
         <is>
-          <t>Uvezivanje kontrolera DEA u krovni sistem nadzora i upravljanja BH Telecom-a (NetEco Management System), sa isporukom licenciranog softverskog paketa, instalacijom u nadzornom centru, uvezivanjem do najbližeg switcha i testiranjem prosljeđivanja alarma.</t>
+          <t>Puštanje u rad kompletnog sistema, funkcionalno testiranje automatskog starta DEA po kriteriju stanja baterija, testiranje prelaska izvora i 72-satni probni rad sa zapisom parametara.</t>
         </is>
       </c>
       <c r="C62" s="128" t="inlineStr">
@@ -3948,12 +3989,12 @@
     <row r="63" s="92">
       <c r="A63" s="128" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B63" s="161" t="inlineStr">
         <is>
-          <t>Obuka osoblja Investitora (do 4 osobe) za rukovanje i osnovno održavanje sistema, u trajanju od min. 1 radnog dana.</t>
+          <t>Uvezivanje kontrolera DEA u krovni sistem nadzora i upravljanja BH Telecom-a (NetEco Management System), sa isporukom licenciranog softverskog paketa, instalacijom u nadzornom centru, uvezivanjem do najbližeg switcha i testiranjem prosljeđivanja alarma.</t>
         </is>
       </c>
       <c r="C63" s="128" t="inlineStr">
@@ -3973,12 +4014,12 @@
     <row r="64" s="92">
       <c r="A64" s="128" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B64" s="161" t="inlineStr">
         <is>
-          <t>Izrada dokumentacije izvedenog stanja za kompletan LOT 2 (elektro, mašinski i građevinski dio), u 3 štampana primjerka i u elektronskoj formi (PDF + izvorni DWG/DOCX).</t>
+          <t>Obuka osoblja Investitora (do 4 osobe) za rukovanje i osnovno održavanje sistema, u trajanju od min. 1 radnog dana.</t>
         </is>
       </c>
       <c r="C64" s="128" t="inlineStr">
@@ -3996,33 +4037,58 @@
       </c>
     </row>
     <row r="65" s="92">
-      <c r="A65" s="135" t="n"/>
-      <c r="B65" s="167" t="inlineStr">
+      <c r="A65" s="128" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B65" s="161" t="inlineStr">
+        <is>
+          <t>Izrada dokumentacije izvedenog stanja za kompletan LOT 2 (elektro, mašinski i građevinski dio), u 3 štampana primjerka i u elektronskoj formi (PDF + izvorni DWG/DOCX).</t>
+        </is>
+      </c>
+      <c r="C65" s="128" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D65" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="131" t="n"/>
+      <c r="F65" s="131">
+        <f>IF(AND(D65&lt;&gt;"",E65&lt;&gt;""),D65*E65,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" s="92">
+      <c r="A66" s="135" t="n"/>
+      <c r="B66" s="167" t="inlineStr">
         <is>
           <t>UKUPNO 6 — PUŠTANJE U RAD, OBUKA I DOKUMENTACIJA:</t>
         </is>
       </c>
-      <c r="C65" s="168" t="n"/>
-      <c r="D65" s="168" t="n"/>
-      <c r="E65" s="137" t="n"/>
-      <c r="F65" s="138">
-        <f>SUM(F61:F64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67" s="92">
-      <c r="A67" s="170" t="n"/>
-      <c r="B67" s="171" t="inlineStr">
+      <c r="C66" s="168" t="n"/>
+      <c r="D66" s="168" t="n"/>
+      <c r="E66" s="137" t="n"/>
+      <c r="F66" s="138">
+        <f>SUM(F62:F65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68" s="92">
+      <c r="A68" s="170" t="n"/>
+      <c r="B68" s="171" t="inlineStr">
         <is>
           <t>UKUPNO LOT 2 — BS HAMZIĆI (bez PDV-a):</t>
         </is>
       </c>
-      <c r="C67" s="168" t="n"/>
-      <c r="D67" s="168" t="n"/>
-      <c r="E67" s="137" t="n"/>
-      <c r="F67" s="172">
-        <f>F36+F57+F65</f>
+      <c r="C68" s="168" t="n"/>
+      <c r="D68" s="168" t="n"/>
+      <c r="E68" s="137" t="n"/>
+      <c r="F68" s="172">
+        <f>F36+F58+F66</f>
         <v/>
       </c>
     </row>
@@ -4130,7 +4196,7 @@
       <c r="D10" s="168" t="n"/>
       <c r="E10" s="137" t="n"/>
       <c r="F10" s="172">
-        <f>'LOT 2 Sjednica'!F66</f>
+        <f>'LOT 2 Sjednica'!F67</f>
         <v/>
       </c>
     </row>
@@ -4145,7 +4211,7 @@
       <c r="D11" s="168" t="n"/>
       <c r="E11" s="137" t="n"/>
       <c r="F11" s="172">
-        <f>'LOT 2 Hamzići'!F67</f>
+        <f>'LOT 2 Hamzići'!F68</f>
         <v/>
       </c>
     </row>

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LOT 2 Sjednica" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LOT 2 Hamzići" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="REKAPITULACIJA LOT 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 2 Sjednica" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 2 Hamzići" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REKAPITULACIJA LOT 2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'LOT 2 Sjednica'!$8:$9</definedName>

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
@@ -2234,12 +2234,14 @@
       </c>
       <c r="B48" s="161" t="inlineStr">
         <is>
-          <t>Snimanje postojećeg stanja i prevezivanje postojećih strujnih krugova na novi GRO iz Tačke 5.6. Obuhvata:
- - snimanje i evidentiranje svih 7 postojećih strujnih krugova postojećeg razvoda, sa mjerenjem opterećenja i izradom jednopolne sheme zatečenog stanja
- - prevezivanje krugova na odgovarajuće izvode novog GRO, sa označavanjem
- - SIGNALNA RASVJETA antenskog stuba h=38 m (krug K7) NE prevezuje se na novi GRO: priključuje se na DC razvod −48 V iz Tačke 5.16, svjetiljka prema Tački 5.17, sa nadzorom ispada i dojavom u sistem daljinskog nadzora — rasvjeta prepreke je trajno noćno opterećenje i ne smije biti isključena prilikom rekonfiguracije napajanja
- - Ponuđač mjeri stvarnu snagu rasvjete prepreke i dostavlja je Kupcu radi provjere energetskog bilansa (Prilog I, Tačka 1)
-Komplet sa spojnim materijalom, oznakama, ispitivanjem i ažuriranom jednopolnom shemom izvedenog stanja.</t>
+          <t>Isporuka, montaža i povezivanje rasvjete i utičnica kontejnera — kontejner je PRAZAN, bez postojećih električnih instalacija. Obuhvata:
+ - 1 kom LED svjetiljka IP65, svjetlosnog toka ≥1500 lm, 230 V iz GRO; druga svjetiljka kontejnera je LED svjetiljka 48 V DC sa prekidačem uz vrata iz Tačke 5.16, koja daje svjetlo i kad agregat ne radi
+ - 2 kom utičnica 230 V / 16 A, IP44
+ - prekidač rasvjete
+ - bezhalogeni kablovi položeni u PVC kanalice, priključak na novi GRO iz Tačke 5.6
+ - postojeća SIGNALNA RASVJETA (rasvjeta stuba) antenskog stuba NE napaja se iz GRO: priključuje se na DC razvod −48 V iz Tačke 5.16, svjetiljka prema Tački 5.17 — rasvjeta stuba je trajno noćno opterećenje i ne smije biti isključena prilikom rekonfiguracije napajanja
+ - Ponuđač mjeri stvarnu snagu rasvjete stuba i dostavlja je Kupcu radi provjere energetskog bilansa (Prilog I, Tačka 1)
+Komplet sa spojnim materijalom, oznakama, ispitivanjem i jednopolnom shemom izvedenog stanja.</t>
         </is>
       </c>
       <c r="C48" s="128" t="inlineStr">
@@ -3665,8 +3667,8 @@
  - 2 kom utičnica 230 V / 16 A, IP44
  - prekidač rasvjete
  - bezhalogeni kablovi položeni u PVC kanalice, priključak na novi GRO iz Tačke 5.6
- - postojeća SIGNALNA RASVJETA (rasvjeta prepreke) antenskog stuba NE napaja se iz GRO: priključuje se na DC razvod −48 V iz Tačke 5.16, svjetiljka prema Tački 5.17 — rasvjeta prepreke je trajno noćno opterećenje i ne smije biti isključena prilikom rekonfiguracije napajanja
- - Ponuđač mjeri stvarnu snagu rasvjete prepreke i dostavlja je Kupcu radi provjere energetskog bilansa (Prilog I, Tačka 1)
+ - postojeća SIGNALNA RASVJETA (rasvjeta stuba) antenskog stuba NE napaja se iz GRO: priključuje se na DC razvod −48 V iz Tačke 5.16, svjetiljka prema Tački 5.17 — rasvjeta stuba je trajno noćno opterećenje i ne smije biti isključena prilikom rekonfiguracije napajanja
+ - Ponuđač mjeri stvarnu snagu rasvjete stuba i dostavlja je Kupcu radi provjere energetskog bilansa (Prilog I, Tačka 1)
 Komplet sa spojnim materijalom, oznakama, ispitivanjem i jednopolnom shemom izvedenog stanja.</t>
         </is>
       </c>

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
@@ -2125,11 +2125,11 @@
         <is>
           <t>Isporuka i montaža NOVOG GLAVNOG RAZVODNOG ORMARA (GRO) — AC RAZVODNA SEKCIJA, za ugradnju u postojeći kontejner. Ormar je zajednička AC razvodna kutija za agregat (DEA), ispravljački sistem (Huawei ICC360-HA1-C1 ili kompatibilan) i ostalu AC opremu kontejnera. DC/solarni razvod NIJE dio ovog ormara — DC rastavljač, osigurači nizova i DC odvodnik prenapona smješteni su u zasebnom PVDB ormaru koji obezbjeđuje Kupac, fizički odvojenom od GRO-a. Ormar zidni sa nosačima, orijentacionih dimenzija 0,60 × 0,25 × 0,80 m (Š×D×V), mehaničke zaštite min. IP66, zabravljen bravom sa višestrukim zaključavanjem, kao Schrack ili ekvivalent. Sa donje strane obezbijediti prostor za uvod kablova sa PG uvodnicama, stezaljkama, elementima za uzemljenje i sabirnicama, komplet ožičeno, sa min. 30 % rezerve za naknadna proširenja.
 AC RAZVOD — AGREGAT I ISPRAVLJAČI:
- - 1 kom 4p tropoložajna sklopka za odabir izvora, 1-0-2, 63 A, sa uvezanim statusom slobodnog kontakta sa kontrolerom agregata (DIG IN); položaje obilježiti: 1-„agregat", 0-„isključeno", 2-„rezerva"
- - 1 kom 3p dvopoložajna sklopka 0-1, 63 A, sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)
+ - 1 kom 4p tropoložajna sklopka za odabir izvora, 1-0-2, 50 A, sa uvezanim statusom slobodnog kontakta sa kontrolerom agregata (DIG IN); položaje obilježiti: 1-„agregat", 0-„isključeno", 2-„rezerva"
+ - 1 kom 3p dvopoložajna sklopka 0-1, 50 A, sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)
  - 3 kom 1p automatski prekidač, C, 32 A, 10 kA, za zaštitu napajanja preko DEA
  - 1 kom odvodnik prenapona AC, KOMBINOVANI TIP 1 + 2 prema EN 61643-11, Iimp ≥12,5 kA (10/350 µs) po polu, Up ≤1,5 kV, 4p, sa signalizacijom za daljinsko očitanje i uvezanim statusom sa kontrolerom agregata. Objekat ima vanjski sistem zaštite od munje (antenski stub h=38 m), pa odvodnik tipa 2 sam po sebi NIJE dovoljan prema EN 62305-4
- - 1 kom 4p zaštitna strujna sklopka (RCD) 63 A / 300 mA, S-tip (selektivna), za cjelokupni napojni krug iza sklopke izvora
+ - 1 kom 4p zaštitna strujna sklopka (RCD) 50 A / 300 mA, S-tip (selektivna), za cjelokupni napojni krug iza sklopke izvora
  - 2 kom 1p+N RCBO 16 A / 30 mA, tip A, za utičnice i rasvjetu kontejnera
  - 1 kom 3p automatski prekidač, C, 32 A, 10 kA, za AC napajanje ispravljačkog sistema
  - 2 kom 1p automatski prekidač, C, 16 A, sa rezervom za ostalu AC opremu kontejnera i buduća proširenja
@@ -3553,11 +3553,11 @@
         <is>
           <t>Isporuka i montaža NOVOG GLAVNOG RAZVODNOG ORMARA (GRO) — AC RAZVODNA SEKCIJA, za ugradnju u postojeći kontejner. Ormar je zajednička AC razvodna kutija za agregat (DEA), ispravljački sistem (Huawei ICC360-HA1-C1 ili kompatibilan) i ostalu AC opremu kontejnera. DC/solarni razvod NIJE dio ovog ormara — DC rastavljač, osigurači nizova i DC odvodnik prenapona smješteni su u zasebnom PVDB ormaru koji obezbjeđuje Kupac, fizički odvojenom od GRO-a. Ormar zidni sa nosačima, za SZ zid jugozapadno od ulaznih vrata (širina zida 0,595 m), širine ≤0,50 m — orijentacionih dimenzija npr. 0,50 × 0,25 × 0,80 m (Š×D×V), mehaničke zaštite min. IP66, zabravljen bravom sa višestrukim zaključavanjem, kao Schrack ili ekvivalent. Sa donje strane obezbijediti prostor za uvod kablova sa PG uvodnicama, stezaljkama, elementima za uzemljenje i sabirnicama, komplet ožičeno, sa min. 30 % rezerve za naknadna proširenja.
 AC RAZVOD — AGREGAT I ISPRAVLJAČI:
- - 1 kom 4p tropoložajna sklopka za odabir izvora, 1-0-2, 63 A, sa uvezanim statusom slobodnog kontakta sa kontrolerom agregata (DIG IN); položaje obilježiti: 1-„agregat", 0-„isključeno", 2-„rezerva"
- - 1 kom 3p dvopoložajna sklopka 0-1, 63 A, sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)
+ - 1 kom 4p tropoložajna sklopka za odabir izvora, 1-0-2, 50 A, sa uvezanim statusom slobodnog kontakta sa kontrolerom agregata (DIG IN); položaje obilježiti: 1-„agregat", 0-„isključeno", 2-„rezerva"
+ - 1 kom 3p dvopoložajna sklopka 0-1, 50 A, sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)
  - 3 kom 1p automatski prekidač, C, 32 A, 10 kA, za zaštitu napajanja preko DEA
  - 1 kom odvodnik prenapona AC, KOMBINOVANI TIP 1 + 2 prema EN 61643-11, Iimp ≥12,5 kA (10/350 µs) po polu, Up ≤1,5 kV, 4p, sa signalizacijom za daljinsko očitanje i uvezanim statusom sa kontrolerom agregata. Objekat ima vanjski sistem zaštite od munje (rešetkasti antenski stub h=32 m, platforme na +3,0 / +12,0 / +30,0 m), pa odvodnik tipa 2 sam po sebi NIJE dovoljan prema EN 62305-4
- - 1 kom 4p zaštitna strujna sklopka (RCD) 63 A / 300 mA, S-tip (selektivna), za cjelokupni napojni krug iza sklopke izvora
+ - 1 kom 4p zaštitna strujna sklopka (RCD) 50 A / 300 mA, S-tip (selektivna), za cjelokupni napojni krug iza sklopke izvora
  - 2 kom 1p+N RCBO 16 A / 30 mA, tip A, za utičnice i rasvjetu kontejnera
  - 1 kom 3p automatski prekidač, C, 32 A, 10 kA, za AC napajanje ispravljačkog sistema
  - 2 kom 1p automatski prekidač, C, 16 A, sa rezervom za ostalu AC opremu kontejnera i buduća proširenja

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 2 - Sjednica i Hamzici.xlsx
@@ -2126,12 +2126,12 @@
           <t>Isporuka i montaža NOVOG GLAVNOG RAZVODNOG ORMARA (GRO) — AC RAZVODNA SEKCIJA, za ugradnju u postojeći kontejner. Ormar je zajednička AC razvodna kutija za agregat (DEA), ispravljački sistem (Huawei ICC360-HA1-C1 ili kompatibilan) i ostalu AC opremu kontejnera. DC/solarni razvod NIJE dio ovog ormara — DC rastavljač, osigurači nizova i DC odvodnik prenapona smješteni su u zasebnom PVDB ormaru koji obezbjeđuje Kupac, fizički odvojenom od GRO-a. Ormar zidni sa nosačima, orijentacionih dimenzija 0,60 × 0,25 × 0,80 m (Š×D×V), mehaničke zaštite min. IP66, zabravljen bravom sa višestrukim zaključavanjem, kao Schrack ili ekvivalent. Sa donje strane obezbijediti prostor za uvod kablova sa PG uvodnicama, stezaljkama, elementima za uzemljenje i sabirnicama, komplet ožičeno, sa min. 30 % rezerve za naknadna proširenja.
 AC RAZVOD — AGREGAT I ISPRAVLJAČI:
  - 1 kom 4p tropoložajna sklopka za odabir izvora, 1-0-2, 50 A, sa uvezanim statusom slobodnog kontakta sa kontrolerom agregata (DIG IN); položaje obilježiti: 1-„agregat", 0-„isključeno", 2-„rezerva"
- - 1 kom 3p dvopoložajna sklopka 0-1, 50 A, sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)
- - 3 kom 1p automatski prekidač, C, 32 A, 10 kA, za zaštitu napajanja preko DEA
+ - 1 kom 4p dvopoložajna sklopka (QS) 0-1, 50 A, sa prekidanjem neutralnog vodiča i sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)
+ - 1 kom 4p (3P+N) kompaktni prekidač (Q1) 32 A, sa podesivim magnetnim okidanjem, za zaštitu napajanja preko DEA; tri nezavisna jednopolna uređaja na trofaznom dovodu NISU prihvatljiva — jednopolno okidanje ostavlja agregat u jednofaznom radu sa dvije faze pod naponom i ne prekida neutralni vodič
  - 1 kom odvodnik prenapona AC, KOMBINOVANI TIP 1 + 2 prema EN 61643-11, Iimp ≥12,5 kA (10/350 µs) po polu, Up ≤1,5 kV, 4p, sa signalizacijom za daljinsko očitanje i uvezanim statusom sa kontrolerom agregata. Objekat ima vanjski sistem zaštite od munje (antenski stub h=38 m), pa odvodnik tipa 2 sam po sebi NIJE dovoljan prema EN 62305-4
- - 1 kom 4p zaštitna strujna sklopka (RCD) 50 A / 300 mA, S-tip (selektivna), za cjelokupni napojni krug iza sklopke izvora
+ - 1 kom 4p zaštitna strujna sklopka (RCD) 50 A / 300 mA, S-tip (selektivna), najmanje TIP A — tip AC NIJE prihvatljiv jer se iza sklopke napajaju prekidački ispravljači; konačan tip prema dokumentaciji proizvođača ispravljačkog sistema; za cjelokupni napojni krug iza sklopke izvora
  - 2 kom 1p+N RCBO 16 A / 30 mA, tip A, za utičnice i rasvjetu kontejnera
- - 1 kom 3p automatski prekidač, C, 32 A, 10 kA, za AC napajanje ispravljačkog sistema
+ - 1 kom 3p automatski prekidač, C, 20 A, 10 kA, za AC napajanje ispravljačkog sistema (projektna struja 14,4 A pri ograničenju ulazne snage ispravljača na 9,5 kW iz Tačke 3.1)
  - 2 kom 1p automatski prekidač, C, 16 A, sa rezervom za ostalu AC opremu kontejnera i buduća proširenja
 NAPOMENA - ZAŠTITA OD INDIREKTNOG DODIRA: agregat je otočni izvor ograničene struje kvara pa prekostrujna zaštita NE MOŽE ostvariti isključenje u vremenu prema IEC 60364-4-41 (0,4 s za 230 V). Zaštita zaštitnom strujnom sklopkom je stoga OBAVEZNA. Sistem uzemljenja je TN-S sa jedinstvenom tačkom spajanja N i PE u ovom ormaru; otpor uzemljenja ≤10 Ω.
 Sve metalne mase ormara koje u normalnom radu nisu pod naponom povezati na sabirnice za izjednačenje potencijala. Uvodi kablova brtvljeni uvodnicama. Izraditi i pričvrstiti gravirane natpisne pločice: „GRO AC — AGREGAT/SOLAR" i oznaku W012 „OPASAN NAPON" prema EN ISO 7010.</t>
@@ -3554,12 +3554,12 @@
           <t>Isporuka i montaža NOVOG GLAVNOG RAZVODNOG ORMARA (GRO) — AC RAZVODNA SEKCIJA, za ugradnju u postojeći kontejner. Ormar je zajednička AC razvodna kutija za agregat (DEA), ispravljački sistem (Huawei ICC360-HA1-C1 ili kompatibilan) i ostalu AC opremu kontejnera. DC/solarni razvod NIJE dio ovog ormara — DC rastavljač, osigurači nizova i DC odvodnik prenapona smješteni su u zasebnom PVDB ormaru koji obezbjeđuje Kupac, fizički odvojenom od GRO-a. Ormar zidni sa nosačima, za SZ zid jugozapadno od ulaznih vrata (širina zida 0,595 m), širine ≤0,50 m — orijentacionih dimenzija npr. 0,50 × 0,25 × 0,80 m (Š×D×V), mehaničke zaštite min. IP66, zabravljen bravom sa višestrukim zaključavanjem, kao Schrack ili ekvivalent. Sa donje strane obezbijediti prostor za uvod kablova sa PG uvodnicama, stezaljkama, elementima za uzemljenje i sabirnicama, komplet ožičeno, sa min. 30 % rezerve za naknadna proširenja.
 AC RAZVOD — AGREGAT I ISPRAVLJAČI:
  - 1 kom 4p tropoložajna sklopka za odabir izvora, 1-0-2, 50 A, sa uvezanim statusom slobodnog kontakta sa kontrolerom agregata (DIG IN); položaje obilježiti: 1-„agregat", 0-„isključeno", 2-„rezerva"
- - 1 kom 3p dvopoložajna sklopka 0-1, 50 A, sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)
- - 3 kom 1p automatski prekidač, C, 32 A, 10 kA, za zaštitu napajanja preko DEA
+ - 1 kom 4p dvopoložajna sklopka (QS) 0-1, 50 A, sa prekidanjem neutralnog vodiča i sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)
+ - 1 kom 4p (3P+N) kompaktni prekidač (Q1) 32 A, sa podesivim magnetnim okidanjem, za zaštitu napajanja preko DEA; tri nezavisna jednopolna uređaja na trofaznom dovodu NISU prihvatljiva — jednopolno okidanje ostavlja agregat u jednofaznom radu sa dvije faze pod naponom i ne prekida neutralni vodič
  - 1 kom odvodnik prenapona AC, KOMBINOVANI TIP 1 + 2 prema EN 61643-11, Iimp ≥12,5 kA (10/350 µs) po polu, Up ≤1,5 kV, 4p, sa signalizacijom za daljinsko očitanje i uvezanim statusom sa kontrolerom agregata. Objekat ima vanjski sistem zaštite od munje (rešetkasti antenski stub h=32 m, platforme na +3,0 / +12,0 / +30,0 m), pa odvodnik tipa 2 sam po sebi NIJE dovoljan prema EN 62305-4
- - 1 kom 4p zaštitna strujna sklopka (RCD) 50 A / 300 mA, S-tip (selektivna), za cjelokupni napojni krug iza sklopke izvora
+ - 1 kom 4p zaštitna strujna sklopka (RCD) 50 A / 300 mA, S-tip (selektivna), najmanje TIP A — tip AC NIJE prihvatljiv jer se iza sklopke napajaju prekidački ispravljači; konačan tip prema dokumentaciji proizvođača ispravljačkog sistema; za cjelokupni napojni krug iza sklopke izvora
  - 2 kom 1p+N RCBO 16 A / 30 mA, tip A, za utičnice i rasvjetu kontejnera
- - 1 kom 3p automatski prekidač, C, 32 A, 10 kA, za AC napajanje ispravljačkog sistema
+ - 1 kom 3p automatski prekidač, C, 20 A, 10 kA, za AC napajanje ispravljačkog sistema (projektna struja 14,4 A pri ograničenju ulazne snage ispravljača na 9,5 kW iz Tačke 3.1)
  - 2 kom 1p automatski prekidač, C, 16 A, sa rezervom za ostalu AC opremu kontejnera i buduća proširenja
 NAPOMENA - ZAŠTITA OD INDIREKTNOG DODIRA: agregat je otočni izvor ograničene struje kvara pa prekostrujna zaštita NE MOŽE ostvariti isključenje u vremenu prema IEC 60364-4-41 (0,4 s za 230 V). Zaštita zaštitnom strujnom sklopkom je stoga OBAVEZNA. Sistem uzemljenja je TN-S sa jedinstvenom tačkom spajanja N i PE u ovom ormaru; otpor uzemljenja ≤10 Ω.
 Sve metalne mase ormara koje u normalnom radu nisu pod naponom povezati na sabirnice za izjednačenje potencijala. Uvodi kablova brtvljeni uvodnicama. Izraditi i pričvrstiti gravirane natpisne pločice: „GRO AC — AGREGAT/SOLAR" i oznaku W012 „OPASAN NAPON" prema EN ISO 7010.</t>
